--- a/Results ang figures/Sizing and Siting Results.xlsx
+++ b/Results ang figures/Sizing and Siting Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikol\OneDrive\Dokumente\Σχολή\Thesis\models\sensitivity analysis\Results ang figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F4F14A-026F-4C7B-B48D-36B239E1822C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF061C97-FE44-4577-882D-C7DDC75DCB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{6DB7FB00-6540-4525-8998-DFC2BB4DB046}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
   <si>
     <t>Planning Results</t>
   </si>
@@ -53,54 +53,6 @@
     <t>Microgrid 1</t>
   </si>
   <si>
-    <t>Node 1</t>
-  </si>
-  <si>
-    <t>Node 2</t>
-  </si>
-  <si>
-    <t>Node 3</t>
-  </si>
-  <si>
-    <t>Node 4</t>
-  </si>
-  <si>
-    <t>Node 5</t>
-  </si>
-  <si>
-    <t>Node 6</t>
-  </si>
-  <si>
-    <t>Node 7</t>
-  </si>
-  <si>
-    <t>Node 8</t>
-  </si>
-  <si>
-    <t>Node 9</t>
-  </si>
-  <si>
-    <t>Node 10</t>
-  </si>
-  <si>
-    <t>Node 11</t>
-  </si>
-  <si>
-    <t>Node 12</t>
-  </si>
-  <si>
-    <t>Node 13</t>
-  </si>
-  <si>
-    <t>Node 14</t>
-  </si>
-  <si>
-    <t>Node 15</t>
-  </si>
-  <si>
-    <t>Node 16</t>
-  </si>
-  <si>
     <t>Microgrid 2</t>
   </si>
   <si>
@@ -108,15 +60,6 @@
   </si>
   <si>
     <t>KW</t>
-  </si>
-  <si>
-    <t>Node 17</t>
-  </si>
-  <si>
-    <t>Node 18</t>
-  </si>
-  <si>
-    <t>Node 19</t>
   </si>
   <si>
     <t>B</t>
@@ -314,7 +257,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -327,13 +270,13 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="1">
+              <a:rPr lang="en-US" sz="1800" b="1">
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>Cooptimization Scenario</a:t>
             </a:r>
-            <a:endParaRPr lang="el-GR" sz="1600" b="1">
+            <a:endParaRPr lang="el-GR" sz="1800" b="1">
               <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:endParaRPr>
@@ -353,7 +296,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -410,115 +353,115 @@
                 <c:ptCount val="37"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="16">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="17">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="18">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="19">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="20">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="21">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="22">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="23">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="24">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="25">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="26">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="27">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="28">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="29">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="30">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="31">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="32">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="33">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="34">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="35">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="36">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -629,115 +572,115 @@
                 <c:ptCount val="37"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="16">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="17">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="18">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="19">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="20">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="21">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="22">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="23">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="24">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="25">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="26">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="27">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="28">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="29">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="30">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="31">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="32">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="33">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="34">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="35">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="36">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -845,115 +788,115 @@
                 <c:ptCount val="37"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="16">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="17">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="18">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="19">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="20">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="21">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="22">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="23">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="24">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="25">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="26">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="27">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="28">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="29">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="30">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="31">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="32">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="33">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="34">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="35">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="36">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1197,7 +1140,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1247,7 +1190,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1260,20 +1203,20 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100">
+                  <a:rPr lang="en-US" sz="1400">
                     <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:rPr>
                   <a:t>Capacity</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
+                  <a:rPr lang="en-US" sz="1400" baseline="0">
                     <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:rPr>
                   <a:t> in MW</a:t>
                 </a:r>
-                <a:endParaRPr lang="el-GR" sz="1100">
+                <a:endParaRPr lang="el-GR" sz="1400">
                   <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:endParaRPr>
@@ -1301,7 +1244,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -1333,7 +1276,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1381,7 +1324,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1572,52 +1515,52 @@
                 <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -2156,52 +2099,52 @@
                 <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -2692,115 +2635,115 @@
                 <c:ptCount val="37"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="16">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="17">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="18">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="19">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="20">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="21">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="22">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="23">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="24">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="25">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="26">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="27">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="28">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="29">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="30">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="31">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="32">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="33">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="34">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="35">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="36">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -3016,115 +2959,115 @@
                       <c:ptCount val="37"/>
                       <c:lvl>
                         <c:pt idx="0">
-                          <c:v>Node 1</c:v>
+                          <c:v>1</c:v>
                         </c:pt>
                         <c:pt idx="1">
-                          <c:v>Node 2</c:v>
+                          <c:v>2</c:v>
                         </c:pt>
                         <c:pt idx="2">
-                          <c:v>Node 3</c:v>
+                          <c:v>3</c:v>
                         </c:pt>
                         <c:pt idx="3">
-                          <c:v>Node 4</c:v>
+                          <c:v>4</c:v>
                         </c:pt>
                         <c:pt idx="4">
-                          <c:v>Node 5</c:v>
+                          <c:v>5</c:v>
                         </c:pt>
                         <c:pt idx="5">
-                          <c:v>Node 6</c:v>
+                          <c:v>6</c:v>
                         </c:pt>
                         <c:pt idx="6">
-                          <c:v>Node 7</c:v>
+                          <c:v>7</c:v>
                         </c:pt>
                         <c:pt idx="7">
-                          <c:v>Node 8</c:v>
+                          <c:v>8</c:v>
                         </c:pt>
                         <c:pt idx="8">
-                          <c:v>Node 9</c:v>
+                          <c:v>9</c:v>
                         </c:pt>
                         <c:pt idx="9">
-                          <c:v>Node 10</c:v>
+                          <c:v>10</c:v>
                         </c:pt>
                         <c:pt idx="10">
-                          <c:v>Node 11</c:v>
+                          <c:v>11</c:v>
                         </c:pt>
                         <c:pt idx="11">
-                          <c:v>Node 12</c:v>
+                          <c:v>12</c:v>
                         </c:pt>
                         <c:pt idx="12">
-                          <c:v>Node 13</c:v>
+                          <c:v>13</c:v>
                         </c:pt>
                         <c:pt idx="13">
-                          <c:v>Node 14</c:v>
+                          <c:v>14</c:v>
                         </c:pt>
                         <c:pt idx="14">
-                          <c:v>Node 15</c:v>
+                          <c:v>15</c:v>
                         </c:pt>
                         <c:pt idx="15">
-                          <c:v>Node 16</c:v>
+                          <c:v>16</c:v>
                         </c:pt>
                         <c:pt idx="16">
-                          <c:v>Node 17</c:v>
+                          <c:v>17</c:v>
                         </c:pt>
                         <c:pt idx="17">
-                          <c:v>Node 18</c:v>
+                          <c:v>18</c:v>
                         </c:pt>
                         <c:pt idx="18">
-                          <c:v>Node 19</c:v>
+                          <c:v>19</c:v>
                         </c:pt>
                         <c:pt idx="19">
-                          <c:v>Node 1</c:v>
+                          <c:v>1</c:v>
                         </c:pt>
                         <c:pt idx="20">
-                          <c:v>Node 2</c:v>
+                          <c:v>2</c:v>
                         </c:pt>
                         <c:pt idx="21">
-                          <c:v>Node 3</c:v>
+                          <c:v>3</c:v>
                         </c:pt>
                         <c:pt idx="22">
-                          <c:v>Node 4</c:v>
+                          <c:v>4</c:v>
                         </c:pt>
                         <c:pt idx="23">
-                          <c:v>Node 5</c:v>
+                          <c:v>5</c:v>
                         </c:pt>
                         <c:pt idx="24">
-                          <c:v>Node 6</c:v>
+                          <c:v>6</c:v>
                         </c:pt>
                         <c:pt idx="25">
-                          <c:v>Node 7</c:v>
+                          <c:v>7</c:v>
                         </c:pt>
                         <c:pt idx="26">
-                          <c:v>Node 8</c:v>
+                          <c:v>8</c:v>
                         </c:pt>
                         <c:pt idx="27">
-                          <c:v>Node 9</c:v>
+                          <c:v>9</c:v>
                         </c:pt>
                         <c:pt idx="28">
-                          <c:v>Node 10</c:v>
+                          <c:v>10</c:v>
                         </c:pt>
                         <c:pt idx="29">
-                          <c:v>Node 11</c:v>
+                          <c:v>11</c:v>
                         </c:pt>
                         <c:pt idx="30">
-                          <c:v>Node 12</c:v>
+                          <c:v>12</c:v>
                         </c:pt>
                         <c:pt idx="31">
-                          <c:v>Node 13</c:v>
+                          <c:v>13</c:v>
                         </c:pt>
                         <c:pt idx="32">
-                          <c:v>Node 14</c:v>
+                          <c:v>14</c:v>
                         </c:pt>
                         <c:pt idx="33">
-                          <c:v>Node 15</c:v>
+                          <c:v>15</c:v>
                         </c:pt>
                         <c:pt idx="34">
-                          <c:v>Node 16</c:v>
+                          <c:v>16</c:v>
                         </c:pt>
                         <c:pt idx="35">
-                          <c:v>Node 17</c:v>
+                          <c:v>17</c:v>
                         </c:pt>
                         <c:pt idx="36">
-                          <c:v>Node 18</c:v>
+                          <c:v>18</c:v>
                         </c:pt>
                       </c:lvl>
                       <c:lvl>
@@ -3661,52 +3604,52 @@
                 <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -4271,52 +4214,52 @@
                 <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -4461,52 +4404,52 @@
                       <c:ptCount val="16"/>
                       <c:lvl>
                         <c:pt idx="0">
-                          <c:v>Node 1</c:v>
+                          <c:v>1</c:v>
                         </c:pt>
                         <c:pt idx="1">
-                          <c:v>Node 3</c:v>
+                          <c:v>3</c:v>
                         </c:pt>
                         <c:pt idx="2">
-                          <c:v>Node 4</c:v>
+                          <c:v>4</c:v>
                         </c:pt>
                         <c:pt idx="3">
-                          <c:v>Node 11</c:v>
+                          <c:v>11</c:v>
                         </c:pt>
                         <c:pt idx="4">
-                          <c:v>Node 12</c:v>
+                          <c:v>12</c:v>
                         </c:pt>
                         <c:pt idx="5">
-                          <c:v>Node 16</c:v>
+                          <c:v>16</c:v>
                         </c:pt>
                         <c:pt idx="6">
-                          <c:v>Node 18</c:v>
+                          <c:v>18</c:v>
                         </c:pt>
                         <c:pt idx="7">
-                          <c:v>Node 19</c:v>
+                          <c:v>19</c:v>
                         </c:pt>
                         <c:pt idx="8">
-                          <c:v>Node 1</c:v>
+                          <c:v>1</c:v>
                         </c:pt>
                         <c:pt idx="9">
-                          <c:v>Node 6</c:v>
+                          <c:v>6</c:v>
                         </c:pt>
                         <c:pt idx="10">
-                          <c:v>Node 7</c:v>
+                          <c:v>7</c:v>
                         </c:pt>
                         <c:pt idx="11">
-                          <c:v>Node 8</c:v>
+                          <c:v>8</c:v>
                         </c:pt>
                         <c:pt idx="12">
-                          <c:v>Node 9</c:v>
+                          <c:v>9</c:v>
                         </c:pt>
                         <c:pt idx="13">
-                          <c:v>Node 10</c:v>
+                          <c:v>10</c:v>
                         </c:pt>
                         <c:pt idx="14">
-                          <c:v>Node 16</c:v>
+                          <c:v>16</c:v>
                         </c:pt>
                         <c:pt idx="15">
-                          <c:v>Node 18</c:v>
+                          <c:v>18</c:v>
                         </c:pt>
                       </c:lvl>
                       <c:lvl>
@@ -5032,115 +4975,115 @@
                 <c:ptCount val="37"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="16">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="17">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="18">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="19">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="20">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="21">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="22">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="23">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="24">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="25">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="26">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="27">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="28">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="29">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="30">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="31">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="32">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="33">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="34">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="35">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="36">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -5337,115 +5280,115 @@
                       <c:ptCount val="37"/>
                       <c:lvl>
                         <c:pt idx="0">
-                          <c:v>Node 1</c:v>
+                          <c:v>1</c:v>
                         </c:pt>
                         <c:pt idx="1">
-                          <c:v>Node 2</c:v>
+                          <c:v>2</c:v>
                         </c:pt>
                         <c:pt idx="2">
-                          <c:v>Node 3</c:v>
+                          <c:v>3</c:v>
                         </c:pt>
                         <c:pt idx="3">
-                          <c:v>Node 4</c:v>
+                          <c:v>4</c:v>
                         </c:pt>
                         <c:pt idx="4">
-                          <c:v>Node 5</c:v>
+                          <c:v>5</c:v>
                         </c:pt>
                         <c:pt idx="5">
-                          <c:v>Node 6</c:v>
+                          <c:v>6</c:v>
                         </c:pt>
                         <c:pt idx="6">
-                          <c:v>Node 7</c:v>
+                          <c:v>7</c:v>
                         </c:pt>
                         <c:pt idx="7">
-                          <c:v>Node 8</c:v>
+                          <c:v>8</c:v>
                         </c:pt>
                         <c:pt idx="8">
-                          <c:v>Node 9</c:v>
+                          <c:v>9</c:v>
                         </c:pt>
                         <c:pt idx="9">
-                          <c:v>Node 10</c:v>
+                          <c:v>10</c:v>
                         </c:pt>
                         <c:pt idx="10">
-                          <c:v>Node 11</c:v>
+                          <c:v>11</c:v>
                         </c:pt>
                         <c:pt idx="11">
-                          <c:v>Node 12</c:v>
+                          <c:v>12</c:v>
                         </c:pt>
                         <c:pt idx="12">
-                          <c:v>Node 13</c:v>
+                          <c:v>13</c:v>
                         </c:pt>
                         <c:pt idx="13">
-                          <c:v>Node 14</c:v>
+                          <c:v>14</c:v>
                         </c:pt>
                         <c:pt idx="14">
-                          <c:v>Node 15</c:v>
+                          <c:v>15</c:v>
                         </c:pt>
                         <c:pt idx="15">
-                          <c:v>Node 16</c:v>
+                          <c:v>16</c:v>
                         </c:pt>
                         <c:pt idx="16">
-                          <c:v>Node 17</c:v>
+                          <c:v>17</c:v>
                         </c:pt>
                         <c:pt idx="17">
-                          <c:v>Node 18</c:v>
+                          <c:v>18</c:v>
                         </c:pt>
                         <c:pt idx="18">
-                          <c:v>Node 19</c:v>
+                          <c:v>19</c:v>
                         </c:pt>
                         <c:pt idx="19">
-                          <c:v>Node 1</c:v>
+                          <c:v>1</c:v>
                         </c:pt>
                         <c:pt idx="20">
-                          <c:v>Node 2</c:v>
+                          <c:v>2</c:v>
                         </c:pt>
                         <c:pt idx="21">
-                          <c:v>Node 3</c:v>
+                          <c:v>3</c:v>
                         </c:pt>
                         <c:pt idx="22">
-                          <c:v>Node 4</c:v>
+                          <c:v>4</c:v>
                         </c:pt>
                         <c:pt idx="23">
-                          <c:v>Node 5</c:v>
+                          <c:v>5</c:v>
                         </c:pt>
                         <c:pt idx="24">
-                          <c:v>Node 6</c:v>
+                          <c:v>6</c:v>
                         </c:pt>
                         <c:pt idx="25">
-                          <c:v>Node 7</c:v>
+                          <c:v>7</c:v>
                         </c:pt>
                         <c:pt idx="26">
-                          <c:v>Node 8</c:v>
+                          <c:v>8</c:v>
                         </c:pt>
                         <c:pt idx="27">
-                          <c:v>Node 9</c:v>
+                          <c:v>9</c:v>
                         </c:pt>
                         <c:pt idx="28">
-                          <c:v>Node 10</c:v>
+                          <c:v>10</c:v>
                         </c:pt>
                         <c:pt idx="29">
-                          <c:v>Node 11</c:v>
+                          <c:v>11</c:v>
                         </c:pt>
                         <c:pt idx="30">
-                          <c:v>Node 12</c:v>
+                          <c:v>12</c:v>
                         </c:pt>
                         <c:pt idx="31">
-                          <c:v>Node 13</c:v>
+                          <c:v>13</c:v>
                         </c:pt>
                         <c:pt idx="32">
-                          <c:v>Node 14</c:v>
+                          <c:v>14</c:v>
                         </c:pt>
                         <c:pt idx="33">
-                          <c:v>Node 15</c:v>
+                          <c:v>15</c:v>
                         </c:pt>
                         <c:pt idx="34">
-                          <c:v>Node 16</c:v>
+                          <c:v>16</c:v>
                         </c:pt>
                         <c:pt idx="35">
-                          <c:v>Node 17</c:v>
+                          <c:v>17</c:v>
                         </c:pt>
                         <c:pt idx="36">
-                          <c:v>Node 18</c:v>
+                          <c:v>18</c:v>
                         </c:pt>
                       </c:lvl>
                       <c:lvl>
@@ -5573,115 +5516,115 @@
                       <c:ptCount val="37"/>
                       <c:lvl>
                         <c:pt idx="0">
-                          <c:v>Node 1</c:v>
+                          <c:v>1</c:v>
                         </c:pt>
                         <c:pt idx="1">
-                          <c:v>Node 2</c:v>
+                          <c:v>2</c:v>
                         </c:pt>
                         <c:pt idx="2">
-                          <c:v>Node 3</c:v>
+                          <c:v>3</c:v>
                         </c:pt>
                         <c:pt idx="3">
-                          <c:v>Node 4</c:v>
+                          <c:v>4</c:v>
                         </c:pt>
                         <c:pt idx="4">
-                          <c:v>Node 5</c:v>
+                          <c:v>5</c:v>
                         </c:pt>
                         <c:pt idx="5">
-                          <c:v>Node 6</c:v>
+                          <c:v>6</c:v>
                         </c:pt>
                         <c:pt idx="6">
-                          <c:v>Node 7</c:v>
+                          <c:v>7</c:v>
                         </c:pt>
                         <c:pt idx="7">
-                          <c:v>Node 8</c:v>
+                          <c:v>8</c:v>
                         </c:pt>
                         <c:pt idx="8">
-                          <c:v>Node 9</c:v>
+                          <c:v>9</c:v>
                         </c:pt>
                         <c:pt idx="9">
-                          <c:v>Node 10</c:v>
+                          <c:v>10</c:v>
                         </c:pt>
                         <c:pt idx="10">
-                          <c:v>Node 11</c:v>
+                          <c:v>11</c:v>
                         </c:pt>
                         <c:pt idx="11">
-                          <c:v>Node 12</c:v>
+                          <c:v>12</c:v>
                         </c:pt>
                         <c:pt idx="12">
-                          <c:v>Node 13</c:v>
+                          <c:v>13</c:v>
                         </c:pt>
                         <c:pt idx="13">
-                          <c:v>Node 14</c:v>
+                          <c:v>14</c:v>
                         </c:pt>
                         <c:pt idx="14">
-                          <c:v>Node 15</c:v>
+                          <c:v>15</c:v>
                         </c:pt>
                         <c:pt idx="15">
-                          <c:v>Node 16</c:v>
+                          <c:v>16</c:v>
                         </c:pt>
                         <c:pt idx="16">
-                          <c:v>Node 17</c:v>
+                          <c:v>17</c:v>
                         </c:pt>
                         <c:pt idx="17">
-                          <c:v>Node 18</c:v>
+                          <c:v>18</c:v>
                         </c:pt>
                         <c:pt idx="18">
-                          <c:v>Node 19</c:v>
+                          <c:v>19</c:v>
                         </c:pt>
                         <c:pt idx="19">
-                          <c:v>Node 1</c:v>
+                          <c:v>1</c:v>
                         </c:pt>
                         <c:pt idx="20">
-                          <c:v>Node 2</c:v>
+                          <c:v>2</c:v>
                         </c:pt>
                         <c:pt idx="21">
-                          <c:v>Node 3</c:v>
+                          <c:v>3</c:v>
                         </c:pt>
                         <c:pt idx="22">
-                          <c:v>Node 4</c:v>
+                          <c:v>4</c:v>
                         </c:pt>
                         <c:pt idx="23">
-                          <c:v>Node 5</c:v>
+                          <c:v>5</c:v>
                         </c:pt>
                         <c:pt idx="24">
-                          <c:v>Node 6</c:v>
+                          <c:v>6</c:v>
                         </c:pt>
                         <c:pt idx="25">
-                          <c:v>Node 7</c:v>
+                          <c:v>7</c:v>
                         </c:pt>
                         <c:pt idx="26">
-                          <c:v>Node 8</c:v>
+                          <c:v>8</c:v>
                         </c:pt>
                         <c:pt idx="27">
-                          <c:v>Node 9</c:v>
+                          <c:v>9</c:v>
                         </c:pt>
                         <c:pt idx="28">
-                          <c:v>Node 10</c:v>
+                          <c:v>10</c:v>
                         </c:pt>
                         <c:pt idx="29">
-                          <c:v>Node 11</c:v>
+                          <c:v>11</c:v>
                         </c:pt>
                         <c:pt idx="30">
-                          <c:v>Node 12</c:v>
+                          <c:v>12</c:v>
                         </c:pt>
                         <c:pt idx="31">
-                          <c:v>Node 13</c:v>
+                          <c:v>13</c:v>
                         </c:pt>
                         <c:pt idx="32">
-                          <c:v>Node 14</c:v>
+                          <c:v>14</c:v>
                         </c:pt>
                         <c:pt idx="33">
-                          <c:v>Node 15</c:v>
+                          <c:v>15</c:v>
                         </c:pt>
                         <c:pt idx="34">
-                          <c:v>Node 16</c:v>
+                          <c:v>16</c:v>
                         </c:pt>
                         <c:pt idx="35">
-                          <c:v>Node 17</c:v>
+                          <c:v>17</c:v>
                         </c:pt>
                         <c:pt idx="36">
-                          <c:v>Node 18</c:v>
+                          <c:v>18</c:v>
                         </c:pt>
                       </c:lvl>
                       <c:lvl>
@@ -5771,6 +5714,183 @@
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Φύλλο1!#REF!</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>#REF!</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Φύλλο1!$D$4:$E$40</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="37"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>8</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>10</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>11</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>13</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>14</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>15</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>16</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>17</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>18</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>19</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>8</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="28">
+                    <c:v>10</c:v>
+                  </c:pt>
+                  <c:pt idx="29">
+                    <c:v>11</c:v>
+                  </c:pt>
+                  <c:pt idx="30">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="31">
+                    <c:v>13</c:v>
+                  </c:pt>
+                  <c:pt idx="32">
+                    <c:v>14</c:v>
+                  </c:pt>
+                  <c:pt idx="33">
+                    <c:v>15</c:v>
+                  </c:pt>
+                  <c:pt idx="34">
+                    <c:v>16</c:v>
+                  </c:pt>
+                  <c:pt idx="35">
+                    <c:v>17</c:v>
+                  </c:pt>
+                  <c:pt idx="36">
+                    <c:v>18</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Microgrid 1</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>Microgrid 2</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Φύλλο1!#REF!</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6BCA-4A3D-A8E7-882E750D07BD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -5783,204 +5903,7 @@
         <c:smooth val="0"/>
         <c:axId val="443852815"/>
         <c:axId val="443845615"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-            <c15:filteredLineSeries>
-              <c15:ser>
-                <c:idx val="3"/>
-                <c:order val="3"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>Φύλλο1!#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>#REF!</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:ln w="28575" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent4"/>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="none"/>
-                </c:marker>
-                <c:cat>
-                  <c:multiLvlStrRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>Φύλλο1!$D$4:$E$40</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:multiLvlStrCache>
-                      <c:ptCount val="37"/>
-                      <c:lvl>
-                        <c:pt idx="0">
-                          <c:v>Node 1</c:v>
-                        </c:pt>
-                        <c:pt idx="1">
-                          <c:v>Node 2</c:v>
-                        </c:pt>
-                        <c:pt idx="2">
-                          <c:v>Node 3</c:v>
-                        </c:pt>
-                        <c:pt idx="3">
-                          <c:v>Node 4</c:v>
-                        </c:pt>
-                        <c:pt idx="4">
-                          <c:v>Node 5</c:v>
-                        </c:pt>
-                        <c:pt idx="5">
-                          <c:v>Node 6</c:v>
-                        </c:pt>
-                        <c:pt idx="6">
-                          <c:v>Node 7</c:v>
-                        </c:pt>
-                        <c:pt idx="7">
-                          <c:v>Node 8</c:v>
-                        </c:pt>
-                        <c:pt idx="8">
-                          <c:v>Node 9</c:v>
-                        </c:pt>
-                        <c:pt idx="9">
-                          <c:v>Node 10</c:v>
-                        </c:pt>
-                        <c:pt idx="10">
-                          <c:v>Node 11</c:v>
-                        </c:pt>
-                        <c:pt idx="11">
-                          <c:v>Node 12</c:v>
-                        </c:pt>
-                        <c:pt idx="12">
-                          <c:v>Node 13</c:v>
-                        </c:pt>
-                        <c:pt idx="13">
-                          <c:v>Node 14</c:v>
-                        </c:pt>
-                        <c:pt idx="14">
-                          <c:v>Node 15</c:v>
-                        </c:pt>
-                        <c:pt idx="15">
-                          <c:v>Node 16</c:v>
-                        </c:pt>
-                        <c:pt idx="16">
-                          <c:v>Node 17</c:v>
-                        </c:pt>
-                        <c:pt idx="17">
-                          <c:v>Node 18</c:v>
-                        </c:pt>
-                        <c:pt idx="18">
-                          <c:v>Node 19</c:v>
-                        </c:pt>
-                        <c:pt idx="19">
-                          <c:v>Node 1</c:v>
-                        </c:pt>
-                        <c:pt idx="20">
-                          <c:v>Node 2</c:v>
-                        </c:pt>
-                        <c:pt idx="21">
-                          <c:v>Node 3</c:v>
-                        </c:pt>
-                        <c:pt idx="22">
-                          <c:v>Node 4</c:v>
-                        </c:pt>
-                        <c:pt idx="23">
-                          <c:v>Node 5</c:v>
-                        </c:pt>
-                        <c:pt idx="24">
-                          <c:v>Node 6</c:v>
-                        </c:pt>
-                        <c:pt idx="25">
-                          <c:v>Node 7</c:v>
-                        </c:pt>
-                        <c:pt idx="26">
-                          <c:v>Node 8</c:v>
-                        </c:pt>
-                        <c:pt idx="27">
-                          <c:v>Node 9</c:v>
-                        </c:pt>
-                        <c:pt idx="28">
-                          <c:v>Node 10</c:v>
-                        </c:pt>
-                        <c:pt idx="29">
-                          <c:v>Node 11</c:v>
-                        </c:pt>
-                        <c:pt idx="30">
-                          <c:v>Node 12</c:v>
-                        </c:pt>
-                        <c:pt idx="31">
-                          <c:v>Node 13</c:v>
-                        </c:pt>
-                        <c:pt idx="32">
-                          <c:v>Node 14</c:v>
-                        </c:pt>
-                        <c:pt idx="33">
-                          <c:v>Node 15</c:v>
-                        </c:pt>
-                        <c:pt idx="34">
-                          <c:v>Node 16</c:v>
-                        </c:pt>
-                        <c:pt idx="35">
-                          <c:v>Node 17</c:v>
-                        </c:pt>
-                        <c:pt idx="36">
-                          <c:v>Node 18</c:v>
-                        </c:pt>
-                      </c:lvl>
-                      <c:lvl>
-                        <c:pt idx="0">
-                          <c:v>Microgrid 1</c:v>
-                        </c:pt>
-                        <c:pt idx="19">
-                          <c:v>Microgrid 2</c:v>
-                        </c:pt>
-                      </c:lvl>
-                    </c:multiLvlStrCache>
-                  </c:multiLvlStrRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>Φύλλο1!#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>1</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:smooth val="1"/>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000003-6BCA-4A3D-A8E7-882E750D07BD}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredLineSeries>
-          </c:ext>
-        </c:extLst>
+        <c:extLst/>
       </c:lineChart>
       <c:catAx>
         <c:axId val="443852815"/>
@@ -6303,7 +6226,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -6316,7 +6239,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" sz="1800"/>
               <a:t>Market Oriented (ESP) Scenario</a:t>
             </a:r>
           </a:p>
@@ -6335,7 +6258,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -6392,115 +6315,115 @@
                 <c:ptCount val="37"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="16">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="17">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="18">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="19">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="20">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="21">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="22">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="23">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="24">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="25">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="26">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="27">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="28">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="29">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="30">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="31">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="32">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="33">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="34">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="35">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="36">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -6611,115 +6534,115 @@
                 <c:ptCount val="37"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="16">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="17">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="18">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="19">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="20">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="21">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="22">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="23">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="24">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="25">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="26">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="27">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="28">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="29">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="30">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="31">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="32">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="33">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="34">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="35">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="36">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -6827,115 +6750,115 @@
                 <c:ptCount val="37"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="16">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="17">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="18">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="19">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="20">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="21">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="22">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="23">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="24">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="25">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="26">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="27">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="28">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="29">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="30">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="31">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="32">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="33">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="34">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="35">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="36">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -7172,7 +7095,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -7222,7 +7145,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -7235,7 +7158,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
+                  <a:rPr lang="en-US" sz="1400"/>
                   <a:t>Capacity in MW</a:t>
                 </a:r>
               </a:p>
@@ -7262,7 +7185,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -7294,7 +7217,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -7342,7 +7265,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -7539,52 +7462,52 @@
                 <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -8072,52 +7995,52 @@
                 <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -8265,52 +8188,52 @@
                       <c:ptCount val="16"/>
                       <c:lvl>
                         <c:pt idx="0">
-                          <c:v>Node 1</c:v>
+                          <c:v>1</c:v>
                         </c:pt>
                         <c:pt idx="1">
-                          <c:v>Node 3</c:v>
+                          <c:v>3</c:v>
                         </c:pt>
                         <c:pt idx="2">
-                          <c:v>Node 4</c:v>
+                          <c:v>4</c:v>
                         </c:pt>
                         <c:pt idx="3">
-                          <c:v>Node 11</c:v>
+                          <c:v>11</c:v>
                         </c:pt>
                         <c:pt idx="4">
-                          <c:v>Node 12</c:v>
+                          <c:v>12</c:v>
                         </c:pt>
                         <c:pt idx="5">
-                          <c:v>Node 16</c:v>
+                          <c:v>16</c:v>
                         </c:pt>
                         <c:pt idx="6">
-                          <c:v>Node 18</c:v>
+                          <c:v>18</c:v>
                         </c:pt>
                         <c:pt idx="7">
-                          <c:v>Node 19</c:v>
+                          <c:v>19</c:v>
                         </c:pt>
                         <c:pt idx="8">
-                          <c:v>Node 1</c:v>
+                          <c:v>1</c:v>
                         </c:pt>
                         <c:pt idx="9">
-                          <c:v>Node 6</c:v>
+                          <c:v>6</c:v>
                         </c:pt>
                         <c:pt idx="10">
-                          <c:v>Node 7</c:v>
+                          <c:v>7</c:v>
                         </c:pt>
                         <c:pt idx="11">
-                          <c:v>Node 8</c:v>
+                          <c:v>8</c:v>
                         </c:pt>
                         <c:pt idx="12">
-                          <c:v>Node 9</c:v>
+                          <c:v>9</c:v>
                         </c:pt>
                         <c:pt idx="13">
-                          <c:v>Node 10</c:v>
+                          <c:v>10</c:v>
                         </c:pt>
                         <c:pt idx="14">
-                          <c:v>Node 16</c:v>
+                          <c:v>16</c:v>
                         </c:pt>
                         <c:pt idx="15">
-                          <c:v>Node 18</c:v>
+                          <c:v>18</c:v>
                         </c:pt>
                       </c:lvl>
                       <c:lvl>
@@ -8756,115 +8679,115 @@
                 <c:ptCount val="37"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="16">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="17">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="18">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="19">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="20">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="21">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="22">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="23">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="24">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="25">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="26">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="27">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="28">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="29">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="30">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="31">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="32">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="33">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="34">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="35">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="36">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -9061,115 +8984,115 @@
                       <c:ptCount val="37"/>
                       <c:lvl>
                         <c:pt idx="0">
-                          <c:v>Node 1</c:v>
+                          <c:v>1</c:v>
                         </c:pt>
                         <c:pt idx="1">
-                          <c:v>Node 2</c:v>
+                          <c:v>2</c:v>
                         </c:pt>
                         <c:pt idx="2">
-                          <c:v>Node 3</c:v>
+                          <c:v>3</c:v>
                         </c:pt>
                         <c:pt idx="3">
-                          <c:v>Node 4</c:v>
+                          <c:v>4</c:v>
                         </c:pt>
                         <c:pt idx="4">
-                          <c:v>Node 5</c:v>
+                          <c:v>5</c:v>
                         </c:pt>
                         <c:pt idx="5">
-                          <c:v>Node 6</c:v>
+                          <c:v>6</c:v>
                         </c:pt>
                         <c:pt idx="6">
-                          <c:v>Node 7</c:v>
+                          <c:v>7</c:v>
                         </c:pt>
                         <c:pt idx="7">
-                          <c:v>Node 8</c:v>
+                          <c:v>8</c:v>
                         </c:pt>
                         <c:pt idx="8">
-                          <c:v>Node 9</c:v>
+                          <c:v>9</c:v>
                         </c:pt>
                         <c:pt idx="9">
-                          <c:v>Node 10</c:v>
+                          <c:v>10</c:v>
                         </c:pt>
                         <c:pt idx="10">
-                          <c:v>Node 11</c:v>
+                          <c:v>11</c:v>
                         </c:pt>
                         <c:pt idx="11">
-                          <c:v>Node 12</c:v>
+                          <c:v>12</c:v>
                         </c:pt>
                         <c:pt idx="12">
-                          <c:v>Node 13</c:v>
+                          <c:v>13</c:v>
                         </c:pt>
                         <c:pt idx="13">
-                          <c:v>Node 14</c:v>
+                          <c:v>14</c:v>
                         </c:pt>
                         <c:pt idx="14">
-                          <c:v>Node 15</c:v>
+                          <c:v>15</c:v>
                         </c:pt>
                         <c:pt idx="15">
-                          <c:v>Node 16</c:v>
+                          <c:v>16</c:v>
                         </c:pt>
                         <c:pt idx="16">
-                          <c:v>Node 17</c:v>
+                          <c:v>17</c:v>
                         </c:pt>
                         <c:pt idx="17">
-                          <c:v>Node 18</c:v>
+                          <c:v>18</c:v>
                         </c:pt>
                         <c:pt idx="18">
-                          <c:v>Node 19</c:v>
+                          <c:v>19</c:v>
                         </c:pt>
                         <c:pt idx="19">
-                          <c:v>Node 1</c:v>
+                          <c:v>1</c:v>
                         </c:pt>
                         <c:pt idx="20">
-                          <c:v>Node 2</c:v>
+                          <c:v>2</c:v>
                         </c:pt>
                         <c:pt idx="21">
-                          <c:v>Node 3</c:v>
+                          <c:v>3</c:v>
                         </c:pt>
                         <c:pt idx="22">
-                          <c:v>Node 4</c:v>
+                          <c:v>4</c:v>
                         </c:pt>
                         <c:pt idx="23">
-                          <c:v>Node 5</c:v>
+                          <c:v>5</c:v>
                         </c:pt>
                         <c:pt idx="24">
-                          <c:v>Node 6</c:v>
+                          <c:v>6</c:v>
                         </c:pt>
                         <c:pt idx="25">
-                          <c:v>Node 7</c:v>
+                          <c:v>7</c:v>
                         </c:pt>
                         <c:pt idx="26">
-                          <c:v>Node 8</c:v>
+                          <c:v>8</c:v>
                         </c:pt>
                         <c:pt idx="27">
-                          <c:v>Node 9</c:v>
+                          <c:v>9</c:v>
                         </c:pt>
                         <c:pt idx="28">
-                          <c:v>Node 10</c:v>
+                          <c:v>10</c:v>
                         </c:pt>
                         <c:pt idx="29">
-                          <c:v>Node 11</c:v>
+                          <c:v>11</c:v>
                         </c:pt>
                         <c:pt idx="30">
-                          <c:v>Node 12</c:v>
+                          <c:v>12</c:v>
                         </c:pt>
                         <c:pt idx="31">
-                          <c:v>Node 13</c:v>
+                          <c:v>13</c:v>
                         </c:pt>
                         <c:pt idx="32">
-                          <c:v>Node 14</c:v>
+                          <c:v>14</c:v>
                         </c:pt>
                         <c:pt idx="33">
-                          <c:v>Node 15</c:v>
+                          <c:v>15</c:v>
                         </c:pt>
                         <c:pt idx="34">
-                          <c:v>Node 16</c:v>
+                          <c:v>16</c:v>
                         </c:pt>
                         <c:pt idx="35">
-                          <c:v>Node 17</c:v>
+                          <c:v>17</c:v>
                         </c:pt>
                         <c:pt idx="36">
-                          <c:v>Node 18</c:v>
+                          <c:v>18</c:v>
                         </c:pt>
                       </c:lvl>
                       <c:lvl>
@@ -9297,115 +9220,115 @@
                       <c:ptCount val="37"/>
                       <c:lvl>
                         <c:pt idx="0">
-                          <c:v>Node 1</c:v>
+                          <c:v>1</c:v>
                         </c:pt>
                         <c:pt idx="1">
-                          <c:v>Node 2</c:v>
+                          <c:v>2</c:v>
                         </c:pt>
                         <c:pt idx="2">
-                          <c:v>Node 3</c:v>
+                          <c:v>3</c:v>
                         </c:pt>
                         <c:pt idx="3">
-                          <c:v>Node 4</c:v>
+                          <c:v>4</c:v>
                         </c:pt>
                         <c:pt idx="4">
-                          <c:v>Node 5</c:v>
+                          <c:v>5</c:v>
                         </c:pt>
                         <c:pt idx="5">
-                          <c:v>Node 6</c:v>
+                          <c:v>6</c:v>
                         </c:pt>
                         <c:pt idx="6">
-                          <c:v>Node 7</c:v>
+                          <c:v>7</c:v>
                         </c:pt>
                         <c:pt idx="7">
-                          <c:v>Node 8</c:v>
+                          <c:v>8</c:v>
                         </c:pt>
                         <c:pt idx="8">
-                          <c:v>Node 9</c:v>
+                          <c:v>9</c:v>
                         </c:pt>
                         <c:pt idx="9">
-                          <c:v>Node 10</c:v>
+                          <c:v>10</c:v>
                         </c:pt>
                         <c:pt idx="10">
-                          <c:v>Node 11</c:v>
+                          <c:v>11</c:v>
                         </c:pt>
                         <c:pt idx="11">
-                          <c:v>Node 12</c:v>
+                          <c:v>12</c:v>
                         </c:pt>
                         <c:pt idx="12">
-                          <c:v>Node 13</c:v>
+                          <c:v>13</c:v>
                         </c:pt>
                         <c:pt idx="13">
-                          <c:v>Node 14</c:v>
+                          <c:v>14</c:v>
                         </c:pt>
                         <c:pt idx="14">
-                          <c:v>Node 15</c:v>
+                          <c:v>15</c:v>
                         </c:pt>
                         <c:pt idx="15">
-                          <c:v>Node 16</c:v>
+                          <c:v>16</c:v>
                         </c:pt>
                         <c:pt idx="16">
-                          <c:v>Node 17</c:v>
+                          <c:v>17</c:v>
                         </c:pt>
                         <c:pt idx="17">
-                          <c:v>Node 18</c:v>
+                          <c:v>18</c:v>
                         </c:pt>
                         <c:pt idx="18">
-                          <c:v>Node 19</c:v>
+                          <c:v>19</c:v>
                         </c:pt>
                         <c:pt idx="19">
-                          <c:v>Node 1</c:v>
+                          <c:v>1</c:v>
                         </c:pt>
                         <c:pt idx="20">
-                          <c:v>Node 2</c:v>
+                          <c:v>2</c:v>
                         </c:pt>
                         <c:pt idx="21">
-                          <c:v>Node 3</c:v>
+                          <c:v>3</c:v>
                         </c:pt>
                         <c:pt idx="22">
-                          <c:v>Node 4</c:v>
+                          <c:v>4</c:v>
                         </c:pt>
                         <c:pt idx="23">
-                          <c:v>Node 5</c:v>
+                          <c:v>5</c:v>
                         </c:pt>
                         <c:pt idx="24">
-                          <c:v>Node 6</c:v>
+                          <c:v>6</c:v>
                         </c:pt>
                         <c:pt idx="25">
-                          <c:v>Node 7</c:v>
+                          <c:v>7</c:v>
                         </c:pt>
                         <c:pt idx="26">
-                          <c:v>Node 8</c:v>
+                          <c:v>8</c:v>
                         </c:pt>
                         <c:pt idx="27">
-                          <c:v>Node 9</c:v>
+                          <c:v>9</c:v>
                         </c:pt>
                         <c:pt idx="28">
-                          <c:v>Node 10</c:v>
+                          <c:v>10</c:v>
                         </c:pt>
                         <c:pt idx="29">
-                          <c:v>Node 11</c:v>
+                          <c:v>11</c:v>
                         </c:pt>
                         <c:pt idx="30">
-                          <c:v>Node 12</c:v>
+                          <c:v>12</c:v>
                         </c:pt>
                         <c:pt idx="31">
-                          <c:v>Node 13</c:v>
+                          <c:v>13</c:v>
                         </c:pt>
                         <c:pt idx="32">
-                          <c:v>Node 14</c:v>
+                          <c:v>14</c:v>
                         </c:pt>
                         <c:pt idx="33">
-                          <c:v>Node 15</c:v>
+                          <c:v>15</c:v>
                         </c:pt>
                         <c:pt idx="34">
-                          <c:v>Node 16</c:v>
+                          <c:v>16</c:v>
                         </c:pt>
                         <c:pt idx="35">
-                          <c:v>Node 17</c:v>
+                          <c:v>17</c:v>
                         </c:pt>
                         <c:pt idx="36">
-                          <c:v>Node 18</c:v>
+                          <c:v>18</c:v>
                         </c:pt>
                       </c:lvl>
                       <c:lvl>
@@ -9495,6 +9418,183 @@
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Φύλλο1!#REF!</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>#REF!</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Φύλλο1!$D$42:$E$78</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="37"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>8</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>10</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>11</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>13</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>14</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>15</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>16</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>17</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>18</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>19</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>8</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="28">
+                    <c:v>10</c:v>
+                  </c:pt>
+                  <c:pt idx="29">
+                    <c:v>11</c:v>
+                  </c:pt>
+                  <c:pt idx="30">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="31">
+                    <c:v>13</c:v>
+                  </c:pt>
+                  <c:pt idx="32">
+                    <c:v>14</c:v>
+                  </c:pt>
+                  <c:pt idx="33">
+                    <c:v>15</c:v>
+                  </c:pt>
+                  <c:pt idx="34">
+                    <c:v>16</c:v>
+                  </c:pt>
+                  <c:pt idx="35">
+                    <c:v>17</c:v>
+                  </c:pt>
+                  <c:pt idx="36">
+                    <c:v>18</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Microgrid 1</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>Microgrid 2</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Φύλλο1!#REF!</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-4099-4147-B1CC-E1D4C5F6C7C5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -9507,204 +9607,7 @@
         <c:smooth val="0"/>
         <c:axId val="441507807"/>
         <c:axId val="441508287"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-            <c15:filteredLineSeries>
-              <c15:ser>
-                <c:idx val="3"/>
-                <c:order val="3"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>Φύλλο1!#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>#REF!</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:ln w="28575" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent4"/>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="none"/>
-                </c:marker>
-                <c:cat>
-                  <c:multiLvlStrRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>Φύλλο1!$D$42:$E$78</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:multiLvlStrCache>
-                      <c:ptCount val="37"/>
-                      <c:lvl>
-                        <c:pt idx="0">
-                          <c:v>Node 1</c:v>
-                        </c:pt>
-                        <c:pt idx="1">
-                          <c:v>Node 2</c:v>
-                        </c:pt>
-                        <c:pt idx="2">
-                          <c:v>Node 3</c:v>
-                        </c:pt>
-                        <c:pt idx="3">
-                          <c:v>Node 4</c:v>
-                        </c:pt>
-                        <c:pt idx="4">
-                          <c:v>Node 5</c:v>
-                        </c:pt>
-                        <c:pt idx="5">
-                          <c:v>Node 6</c:v>
-                        </c:pt>
-                        <c:pt idx="6">
-                          <c:v>Node 7</c:v>
-                        </c:pt>
-                        <c:pt idx="7">
-                          <c:v>Node 8</c:v>
-                        </c:pt>
-                        <c:pt idx="8">
-                          <c:v>Node 9</c:v>
-                        </c:pt>
-                        <c:pt idx="9">
-                          <c:v>Node 10</c:v>
-                        </c:pt>
-                        <c:pt idx="10">
-                          <c:v>Node 11</c:v>
-                        </c:pt>
-                        <c:pt idx="11">
-                          <c:v>Node 12</c:v>
-                        </c:pt>
-                        <c:pt idx="12">
-                          <c:v>Node 13</c:v>
-                        </c:pt>
-                        <c:pt idx="13">
-                          <c:v>Node 14</c:v>
-                        </c:pt>
-                        <c:pt idx="14">
-                          <c:v>Node 15</c:v>
-                        </c:pt>
-                        <c:pt idx="15">
-                          <c:v>Node 16</c:v>
-                        </c:pt>
-                        <c:pt idx="16">
-                          <c:v>Node 17</c:v>
-                        </c:pt>
-                        <c:pt idx="17">
-                          <c:v>Node 18</c:v>
-                        </c:pt>
-                        <c:pt idx="18">
-                          <c:v>Node 19</c:v>
-                        </c:pt>
-                        <c:pt idx="19">
-                          <c:v>Node 1</c:v>
-                        </c:pt>
-                        <c:pt idx="20">
-                          <c:v>Node 2</c:v>
-                        </c:pt>
-                        <c:pt idx="21">
-                          <c:v>Node 3</c:v>
-                        </c:pt>
-                        <c:pt idx="22">
-                          <c:v>Node 4</c:v>
-                        </c:pt>
-                        <c:pt idx="23">
-                          <c:v>Node 5</c:v>
-                        </c:pt>
-                        <c:pt idx="24">
-                          <c:v>Node 6</c:v>
-                        </c:pt>
-                        <c:pt idx="25">
-                          <c:v>Node 7</c:v>
-                        </c:pt>
-                        <c:pt idx="26">
-                          <c:v>Node 8</c:v>
-                        </c:pt>
-                        <c:pt idx="27">
-                          <c:v>Node 9</c:v>
-                        </c:pt>
-                        <c:pt idx="28">
-                          <c:v>Node 10</c:v>
-                        </c:pt>
-                        <c:pt idx="29">
-                          <c:v>Node 11</c:v>
-                        </c:pt>
-                        <c:pt idx="30">
-                          <c:v>Node 12</c:v>
-                        </c:pt>
-                        <c:pt idx="31">
-                          <c:v>Node 13</c:v>
-                        </c:pt>
-                        <c:pt idx="32">
-                          <c:v>Node 14</c:v>
-                        </c:pt>
-                        <c:pt idx="33">
-                          <c:v>Node 15</c:v>
-                        </c:pt>
-                        <c:pt idx="34">
-                          <c:v>Node 16</c:v>
-                        </c:pt>
-                        <c:pt idx="35">
-                          <c:v>Node 17</c:v>
-                        </c:pt>
-                        <c:pt idx="36">
-                          <c:v>Node 18</c:v>
-                        </c:pt>
-                      </c:lvl>
-                      <c:lvl>
-                        <c:pt idx="0">
-                          <c:v>Microgrid 1</c:v>
-                        </c:pt>
-                        <c:pt idx="19">
-                          <c:v>Microgrid 2</c:v>
-                        </c:pt>
-                      </c:lvl>
-                    </c:multiLvlStrCache>
-                  </c:multiLvlStrRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>Φύλλο1!#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>1</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:smooth val="1"/>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000003-4099-4147-B1CC-E1D4C5F6C7C5}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredLineSeries>
-          </c:ext>
-        </c:extLst>
+        <c:extLst/>
       </c:lineChart>
       <c:catAx>
         <c:axId val="441507807"/>
@@ -10034,7 +9937,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -10047,7 +9950,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" sz="1800"/>
               <a:t>Regulated (DSO) Scenario</a:t>
             </a:r>
           </a:p>
@@ -10066,7 +9969,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -10123,115 +10026,115 @@
                 <c:ptCount val="37"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="16">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="17">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="18">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="19">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="20">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="21">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="22">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="23">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="24">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="25">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="26">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="27">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="28">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="29">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="30">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="31">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="32">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="33">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="34">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="35">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="36">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -10342,115 +10245,115 @@
                 <c:ptCount val="37"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="16">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="17">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="18">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="19">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="20">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="21">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="22">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="23">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="24">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="25">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="26">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="27">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="28">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="29">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="30">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="31">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="32">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="33">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="34">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="35">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="36">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -10558,115 +10461,115 @@
                 <c:ptCount val="37"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="16">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="17">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                   <c:pt idx="18">
-                    <c:v>Node 19</c:v>
+                    <c:v>19</c:v>
                   </c:pt>
                   <c:pt idx="19">
-                    <c:v>Node 1</c:v>
+                    <c:v>1</c:v>
                   </c:pt>
                   <c:pt idx="20">
-                    <c:v>Node 2</c:v>
+                    <c:v>2</c:v>
                   </c:pt>
                   <c:pt idx="21">
-                    <c:v>Node 3</c:v>
+                    <c:v>3</c:v>
                   </c:pt>
                   <c:pt idx="22">
-                    <c:v>Node 4</c:v>
+                    <c:v>4</c:v>
                   </c:pt>
                   <c:pt idx="23">
-                    <c:v>Node 5</c:v>
+                    <c:v>5</c:v>
                   </c:pt>
                   <c:pt idx="24">
-                    <c:v>Node 6</c:v>
+                    <c:v>6</c:v>
                   </c:pt>
                   <c:pt idx="25">
-                    <c:v>Node 7</c:v>
+                    <c:v>7</c:v>
                   </c:pt>
                   <c:pt idx="26">
-                    <c:v>Node 8</c:v>
+                    <c:v>8</c:v>
                   </c:pt>
                   <c:pt idx="27">
-                    <c:v>Node 9</c:v>
+                    <c:v>9</c:v>
                   </c:pt>
                   <c:pt idx="28">
-                    <c:v>Node 10</c:v>
+                    <c:v>10</c:v>
                   </c:pt>
                   <c:pt idx="29">
-                    <c:v>Node 11</c:v>
+                    <c:v>11</c:v>
                   </c:pt>
                   <c:pt idx="30">
-                    <c:v>Node 12</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="31">
-                    <c:v>Node 13</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="32">
-                    <c:v>Node 14</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="33">
-                    <c:v>Node 15</c:v>
+                    <c:v>15</c:v>
                   </c:pt>
                   <c:pt idx="34">
-                    <c:v>Node 16</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="35">
-                    <c:v>Node 17</c:v>
+                    <c:v>17</c:v>
                   </c:pt>
                   <c:pt idx="36">
-                    <c:v>Node 18</c:v>
+                    <c:v>18</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -10903,7 +10806,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -10953,7 +10856,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -10966,7 +10869,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
+                  <a:rPr lang="en-US" sz="1400"/>
                   <a:t>Capacity in MW</a:t>
                 </a:r>
               </a:p>
@@ -10993,7 +10896,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -11025,7 +10928,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -11073,7 +10976,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -20450,18 +20353,18 @@
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
@@ -20471,8 +20374,8 @@
       <c r="D4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>4</v>
+      <c r="E4" s="2">
+        <v>1</v>
       </c>
       <c r="F4" s="5">
         <v>10</v>
@@ -20489,8 +20392,8 @@
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
-        <v>5</v>
+      <c r="E5" s="2">
+        <v>2</v>
       </c>
       <c r="F5" s="5">
         <v>10</v>
@@ -20505,8 +20408,8 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
+      <c r="E6" s="2">
+        <v>3</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5">
@@ -20521,8 +20424,8 @@
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>7</v>
+      <c r="E7" s="2">
+        <v>4</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5">
@@ -20537,8 +20440,8 @@
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
-        <v>8</v>
+      <c r="E8" s="2">
+        <v>5</v>
       </c>
       <c r="F8" s="5">
         <v>5.8</v>
@@ -20553,8 +20456,8 @@
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>9</v>
+      <c r="E9" s="2">
+        <v>6</v>
       </c>
       <c r="F9" s="5">
         <v>0</v>
@@ -20569,8 +20472,8 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="2" t="s">
-        <v>10</v>
+      <c r="E10" s="2">
+        <v>7</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -20583,8 +20486,8 @@
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
-        <v>11</v>
+      <c r="E11" s="2">
+        <v>8</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
@@ -20597,8 +20500,8 @@
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
-        <v>12</v>
+      <c r="E12" s="2">
+        <v>9</v>
       </c>
       <c r="F12" s="5">
         <v>10</v>
@@ -20613,8 +20516,8 @@
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="2" t="s">
-        <v>13</v>
+      <c r="E13" s="2">
+        <v>10</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -20627,8 +20530,8 @@
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="2" t="s">
-        <v>14</v>
+      <c r="E14" s="2">
+        <v>11</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5">
@@ -20643,8 +20546,8 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="2" t="s">
-        <v>15</v>
+      <c r="E15" s="2">
+        <v>12</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5">
@@ -20659,8 +20562,8 @@
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="2" t="s">
-        <v>16</v>
+      <c r="E16" s="2">
+        <v>13</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -20673,8 +20576,8 @@
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="2" t="s">
-        <v>17</v>
+      <c r="E17" s="2">
+        <v>14</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -20687,8 +20590,8 @@
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="2" t="s">
-        <v>18</v>
+      <c r="E18" s="2">
+        <v>15</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -20701,8 +20604,8 @@
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="2" t="s">
-        <v>19</v>
+      <c r="E19" s="2">
+        <v>16</v>
       </c>
       <c r="F19" s="5">
         <v>0</v>
@@ -20719,8 +20622,8 @@
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="2" t="s">
-        <v>23</v>
+      <c r="E20" s="2">
+        <v>17</v>
       </c>
       <c r="F20" s="5">
         <v>0.15</v>
@@ -20735,8 +20638,8 @@
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="2" t="s">
-        <v>24</v>
+      <c r="E21" s="2">
+        <v>18</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5">
@@ -20751,8 +20654,8 @@
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="2" t="s">
-        <v>25</v>
+      <c r="E22" s="2">
+        <v>19</v>
       </c>
       <c r="F22" s="5">
         <v>0</v>
@@ -20769,10 +20672,10 @@
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5">
@@ -20787,8 +20690,8 @@
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="2" t="s">
-        <v>5</v>
+      <c r="E24" s="2">
+        <v>2</v>
       </c>
       <c r="F24" s="5">
         <v>0</v>
@@ -20803,8 +20706,8 @@
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
+      <c r="E25" s="2">
+        <v>3</v>
       </c>
       <c r="F25" s="5">
         <v>0</v>
@@ -20819,8 +20722,8 @@
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="2" t="s">
-        <v>7</v>
+      <c r="E26" s="2">
+        <v>4</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -20833,8 +20736,8 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="2" t="s">
-        <v>8</v>
+      <c r="E27" s="2">
+        <v>5</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -20847,8 +20750,8 @@
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="2" t="s">
-        <v>9</v>
+      <c r="E28" s="2">
+        <v>6</v>
       </c>
       <c r="F28" s="5">
         <v>0</v>
@@ -20865,8 +20768,8 @@
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="2" t="s">
-        <v>10</v>
+      <c r="E29" s="2">
+        <v>7</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5">
@@ -20881,8 +20784,8 @@
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="2" t="s">
-        <v>11</v>
+      <c r="E30" s="2">
+        <v>8</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5">
@@ -20897,8 +20800,8 @@
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="2" t="s">
-        <v>12</v>
+      <c r="E31" s="2">
+        <v>9</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
@@ -20913,8 +20816,8 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="2" t="s">
-        <v>13</v>
+      <c r="E32" s="2">
+        <v>10</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5">
@@ -20929,8 +20832,8 @@
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="2" t="s">
-        <v>14</v>
+      <c r="E33" s="2">
+        <v>11</v>
       </c>
       <c r="F33" s="5">
         <v>10</v>
@@ -20945,8 +20848,8 @@
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="2" t="s">
-        <v>15</v>
+      <c r="E34" s="2">
+        <v>12</v>
       </c>
       <c r="F34" s="5">
         <v>0.05</v>
@@ -20961,8 +20864,8 @@
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="2" t="s">
-        <v>16</v>
+      <c r="E35" s="2">
+        <v>13</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -20972,8 +20875,8 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D36" s="2"/>
-      <c r="E36" s="2" t="s">
-        <v>17</v>
+      <c r="E36" s="2">
+        <v>14</v>
       </c>
       <c r="F36" s="5">
         <v>0</v>
@@ -20985,8 +20888,8 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D37" s="2"/>
-      <c r="E37" s="2" t="s">
-        <v>18</v>
+      <c r="E37" s="2">
+        <v>15</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -20996,8 +20899,8 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D38" s="2"/>
-      <c r="E38" s="2" t="s">
-        <v>19</v>
+      <c r="E38" s="2">
+        <v>16</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5">
@@ -21009,8 +20912,8 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D39" s="2"/>
-      <c r="E39" s="2" t="s">
-        <v>23</v>
+      <c r="E39" s="2">
+        <v>17</v>
       </c>
       <c r="F39" s="5">
         <v>0</v>
@@ -21022,8 +20925,8 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D40" s="2"/>
-      <c r="E40" s="2" t="s">
-        <v>24</v>
+      <c r="E40" s="2">
+        <v>18</v>
       </c>
       <c r="F40" s="5">
         <v>0</v>
@@ -21037,18 +20940,18 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C41" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.45">
@@ -21056,8 +20959,8 @@
       <c r="D42" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>4</v>
+      <c r="E42" s="2">
+        <v>1</v>
       </c>
       <c r="F42" s="5">
         <v>10</v>
@@ -21072,8 +20975,8 @@
     <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C43" s="1"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="2" t="s">
-        <v>5</v>
+      <c r="E43" s="2">
+        <v>2</v>
       </c>
       <c r="F43" s="5">
         <v>10</v>
@@ -21086,8 +20989,8 @@
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C44" s="1"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
+      <c r="E44" s="2">
+        <v>3</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5">
@@ -21100,8 +21003,8 @@
     <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C45" s="1"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="2" t="s">
-        <v>7</v>
+      <c r="E45" s="2">
+        <v>4</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5">
@@ -21114,8 +21017,8 @@
     <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C46" s="1"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="2" t="s">
-        <v>8</v>
+      <c r="E46" s="2">
+        <v>5</v>
       </c>
       <c r="F46" s="5">
         <v>10</v>
@@ -21128,8 +21031,8 @@
     <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C47" s="1"/>
       <c r="D47" s="2"/>
-      <c r="E47" s="2" t="s">
-        <v>9</v>
+      <c r="E47" s="2">
+        <v>6</v>
       </c>
       <c r="F47" s="5">
         <v>10</v>
@@ -21142,8 +21045,8 @@
     <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C48" s="1"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="2" t="s">
-        <v>10</v>
+      <c r="E48" s="2">
+        <v>7</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -21154,8 +21057,8 @@
     <row r="49" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C49" s="1"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="2" t="s">
-        <v>11</v>
+      <c r="E49" s="2">
+        <v>8</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -21166,8 +21069,8 @@
     <row r="50" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C50" s="1"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="2" t="s">
-        <v>12</v>
+      <c r="E50" s="2">
+        <v>9</v>
       </c>
       <c r="F50" s="5">
         <v>10</v>
@@ -21180,8 +21083,8 @@
     <row r="51" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C51" s="1"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="2" t="s">
-        <v>13</v>
+      <c r="E51" s="2">
+        <v>10</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -21192,8 +21095,8 @@
     <row r="52" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C52" s="1"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="2" t="s">
-        <v>14</v>
+      <c r="E52" s="2">
+        <v>11</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5">
@@ -21206,8 +21109,8 @@
     <row r="53" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C53" s="1"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="2" t="s">
-        <v>15</v>
+      <c r="E53" s="2">
+        <v>12</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5">
@@ -21220,8 +21123,8 @@
     <row r="54" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C54" s="1"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="2" t="s">
-        <v>16</v>
+      <c r="E54" s="2">
+        <v>13</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -21232,8 +21135,8 @@
     <row r="55" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C55" s="1"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="2" t="s">
-        <v>17</v>
+      <c r="E55" s="2">
+        <v>14</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -21244,8 +21147,8 @@
     <row r="56" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C56" s="1"/>
       <c r="D56" s="2"/>
-      <c r="E56" s="2" t="s">
-        <v>18</v>
+      <c r="E56" s="2">
+        <v>15</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -21256,8 +21159,8 @@
     <row r="57" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C57" s="1"/>
       <c r="D57" s="2"/>
-      <c r="E57" s="2" t="s">
-        <v>19</v>
+      <c r="E57" s="2">
+        <v>16</v>
       </c>
       <c r="F57" s="5">
         <v>0.15</v>
@@ -21272,8 +21175,8 @@
     <row r="58" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C58" s="1"/>
       <c r="D58" s="2"/>
-      <c r="E58" s="2" t="s">
-        <v>23</v>
+      <c r="E58" s="2">
+        <v>17</v>
       </c>
       <c r="F58" s="5">
         <v>0</v>
@@ -21286,8 +21189,8 @@
     <row r="59" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C59" s="1"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="2" t="s">
-        <v>24</v>
+      <c r="E59" s="2">
+        <v>18</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5">
@@ -21300,8 +21203,8 @@
     <row r="60" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C60" s="1"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="2" t="s">
-        <v>25</v>
+      <c r="E60" s="2">
+        <v>19</v>
       </c>
       <c r="F60" s="5">
         <v>0</v>
@@ -21316,10 +21219,10 @@
     <row r="61" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C61" s="1"/>
       <c r="D61" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E61" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="E61" s="2">
+        <v>1</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5">
@@ -21332,8 +21235,8 @@
     <row r="62" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C62" s="1"/>
       <c r="D62" s="2"/>
-      <c r="E62" s="2" t="s">
-        <v>5</v>
+      <c r="E62" s="2">
+        <v>2</v>
       </c>
       <c r="F62" s="5">
         <v>10</v>
@@ -21346,8 +21249,8 @@
     <row r="63" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C63" s="1"/>
       <c r="D63" s="2"/>
-      <c r="E63" s="2" t="s">
-        <v>6</v>
+      <c r="E63" s="2">
+        <v>3</v>
       </c>
       <c r="F63" s="5">
         <v>10</v>
@@ -21360,8 +21263,8 @@
     <row r="64" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C64" s="1"/>
       <c r="D64" s="2"/>
-      <c r="E64" s="2" t="s">
-        <v>7</v>
+      <c r="E64" s="2">
+        <v>4</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -21372,8 +21275,8 @@
     <row r="65" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C65" s="1"/>
       <c r="D65" s="2"/>
-      <c r="E65" s="2" t="s">
-        <v>8</v>
+      <c r="E65" s="2">
+        <v>5</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -21384,8 +21287,8 @@
     <row r="66" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C66" s="1"/>
       <c r="D66" s="2"/>
-      <c r="E66" s="2" t="s">
-        <v>9</v>
+      <c r="E66" s="2">
+        <v>6</v>
       </c>
       <c r="F66" s="5">
         <v>10</v>
@@ -21400,8 +21303,8 @@
     <row r="67" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C67" s="1"/>
       <c r="D67" s="2"/>
-      <c r="E67" s="2" t="s">
-        <v>10</v>
+      <c r="E67" s="2">
+        <v>7</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5">
@@ -21414,8 +21317,8 @@
     <row r="68" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C68" s="1"/>
       <c r="D68" s="2"/>
-      <c r="E68" s="2" t="s">
-        <v>11</v>
+      <c r="E68" s="2">
+        <v>8</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5">
@@ -21428,8 +21331,8 @@
     <row r="69" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C69" s="1"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="2" t="s">
-        <v>12</v>
+      <c r="E69" s="2">
+        <v>9</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5">
@@ -21442,8 +21345,8 @@
     <row r="70" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C70" s="1"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="2" t="s">
-        <v>13</v>
+      <c r="E70" s="2">
+        <v>10</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5">
@@ -21456,8 +21359,8 @@
     <row r="71" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C71" s="1"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="2" t="s">
-        <v>14</v>
+      <c r="E71" s="2">
+        <v>11</v>
       </c>
       <c r="F71" s="5">
         <v>10</v>
@@ -21470,8 +21373,8 @@
     <row r="72" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C72" s="1"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="2" t="s">
-        <v>15</v>
+      <c r="E72" s="2">
+        <v>12</v>
       </c>
       <c r="F72" s="5">
         <v>10</v>
@@ -21484,8 +21387,8 @@
     <row r="73" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C73" s="1"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="2" t="s">
-        <v>16</v>
+      <c r="E73" s="2">
+        <v>13</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -21495,8 +21398,8 @@
     </row>
     <row r="74" spans="3:8" x14ac:dyDescent="0.45">
       <c r="D74" s="2"/>
-      <c r="E74" s="2" t="s">
-        <v>17</v>
+      <c r="E74" s="2">
+        <v>14</v>
       </c>
       <c r="F74" s="5">
         <v>10</v>
@@ -21508,8 +21411,8 @@
     </row>
     <row r="75" spans="3:8" x14ac:dyDescent="0.45">
       <c r="D75" s="2"/>
-      <c r="E75" s="2" t="s">
-        <v>18</v>
+      <c r="E75" s="2">
+        <v>15</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
@@ -21519,8 +21422,8 @@
     </row>
     <row r="76" spans="3:8" x14ac:dyDescent="0.45">
       <c r="D76" s="2"/>
-      <c r="E76" s="2" t="s">
-        <v>19</v>
+      <c r="E76" s="2">
+        <v>16</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5">
@@ -21532,8 +21435,8 @@
     </row>
     <row r="77" spans="3:8" x14ac:dyDescent="0.45">
       <c r="D77" s="2"/>
-      <c r="E77" s="2" t="s">
-        <v>23</v>
+      <c r="E77" s="2">
+        <v>17</v>
       </c>
       <c r="F77" s="5">
         <v>0</v>
@@ -21545,8 +21448,8 @@
     </row>
     <row r="78" spans="3:8" x14ac:dyDescent="0.45">
       <c r="D78" s="2"/>
-      <c r="E78" s="2" t="s">
-        <v>24</v>
+      <c r="E78" s="2">
+        <v>18</v>
       </c>
       <c r="F78" s="5">
         <v>0</v>
@@ -21565,13 +21468,13 @@
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="3:8" x14ac:dyDescent="0.45">
@@ -21579,8 +21482,8 @@
       <c r="D80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>4</v>
+      <c r="E80" s="2">
+        <v>1</v>
       </c>
       <c r="F80" s="5">
         <v>9.8000000000000007</v>
@@ -21595,8 +21498,8 @@
     <row r="81" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C81" s="1"/>
       <c r="D81" s="2"/>
-      <c r="E81" s="2" t="s">
-        <v>5</v>
+      <c r="E81" s="2">
+        <v>2</v>
       </c>
       <c r="F81" s="5">
         <v>10</v>
@@ -21609,8 +21512,8 @@
     <row r="82" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C82" s="1"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="2" t="s">
-        <v>6</v>
+      <c r="E82" s="2">
+        <v>3</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5">
@@ -21623,8 +21526,8 @@
     <row r="83" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C83" s="1"/>
       <c r="D83" s="2"/>
-      <c r="E83" s="2" t="s">
-        <v>7</v>
+      <c r="E83" s="2">
+        <v>4</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5">
@@ -21637,8 +21540,8 @@
     <row r="84" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C84" s="1"/>
       <c r="D84" s="2"/>
-      <c r="E84" s="2" t="s">
-        <v>8</v>
+      <c r="E84" s="2">
+        <v>5</v>
       </c>
       <c r="F84" s="5">
         <v>0</v>
@@ -21651,8 +21554,8 @@
     <row r="85" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C85" s="1"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="2" t="s">
-        <v>9</v>
+      <c r="E85" s="2">
+        <v>6</v>
       </c>
       <c r="F85" s="5">
         <v>0.35</v>
@@ -21665,8 +21568,8 @@
     <row r="86" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C86" s="1"/>
       <c r="D86" s="2"/>
-      <c r="E86" s="2" t="s">
-        <v>10</v>
+      <c r="E86" s="2">
+        <v>7</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
@@ -21677,8 +21580,8 @@
     <row r="87" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C87" s="1"/>
       <c r="D87" s="2"/>
-      <c r="E87" s="2" t="s">
-        <v>11</v>
+      <c r="E87" s="2">
+        <v>8</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
@@ -21689,8 +21592,8 @@
     <row r="88" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C88" s="1"/>
       <c r="D88" s="2"/>
-      <c r="E88" s="2" t="s">
-        <v>12</v>
+      <c r="E88" s="2">
+        <v>9</v>
       </c>
       <c r="F88" s="5">
         <v>9</v>
@@ -21703,8 +21606,8 @@
     <row r="89" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C89" s="1"/>
       <c r="D89" s="2"/>
-      <c r="E89" s="2" t="s">
-        <v>13</v>
+      <c r="E89" s="2">
+        <v>10</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
@@ -21715,8 +21618,8 @@
     <row r="90" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C90" s="1"/>
       <c r="D90" s="2"/>
-      <c r="E90" s="2" t="s">
-        <v>14</v>
+      <c r="E90" s="2">
+        <v>11</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="5">
@@ -21729,8 +21632,8 @@
     <row r="91" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C91" s="1"/>
       <c r="D91" s="2"/>
-      <c r="E91" s="2" t="s">
-        <v>15</v>
+      <c r="E91" s="2">
+        <v>12</v>
       </c>
       <c r="F91" s="5"/>
       <c r="G91" s="5">
@@ -21743,8 +21646,8 @@
     <row r="92" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C92" s="1"/>
       <c r="D92" s="2"/>
-      <c r="E92" s="2" t="s">
-        <v>16</v>
+      <c r="E92" s="2">
+        <v>13</v>
       </c>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
@@ -21755,8 +21658,8 @@
     <row r="93" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C93" s="1"/>
       <c r="D93" s="2"/>
-      <c r="E93" s="2" t="s">
-        <v>17</v>
+      <c r="E93" s="2">
+        <v>14</v>
       </c>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
@@ -21767,8 +21670,8 @@
     <row r="94" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C94" s="1"/>
       <c r="D94" s="2"/>
-      <c r="E94" s="2" t="s">
-        <v>18</v>
+      <c r="E94" s="2">
+        <v>15</v>
       </c>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
@@ -21779,8 +21682,8 @@
     <row r="95" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C95" s="1"/>
       <c r="D95" s="2"/>
-      <c r="E95" s="2" t="s">
-        <v>19</v>
+      <c r="E95" s="2">
+        <v>16</v>
       </c>
       <c r="F95" s="5">
         <v>10</v>
@@ -21795,8 +21698,8 @@
     <row r="96" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C96" s="1"/>
       <c r="D96" s="2"/>
-      <c r="E96" s="2" t="s">
-        <v>23</v>
+      <c r="E96" s="2">
+        <v>17</v>
       </c>
       <c r="F96" s="5">
         <v>2.4500000000000002</v>
@@ -21809,8 +21712,8 @@
     <row r="97" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C97" s="1"/>
       <c r="D97" s="2"/>
-      <c r="E97" s="2" t="s">
-        <v>24</v>
+      <c r="E97" s="2">
+        <v>18</v>
       </c>
       <c r="F97" s="5"/>
       <c r="G97" s="5">
@@ -21823,8 +21726,8 @@
     <row r="98" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C98" s="1"/>
       <c r="D98" s="2"/>
-      <c r="E98" s="2" t="s">
-        <v>25</v>
+      <c r="E98" s="2">
+        <v>19</v>
       </c>
       <c r="F98" s="5">
         <v>0</v>
@@ -21839,10 +21742,10 @@
     <row r="99" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C99" s="1"/>
       <c r="D99" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E99" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="E99" s="2">
+        <v>1</v>
       </c>
       <c r="F99" s="5"/>
       <c r="G99" s="5">
@@ -21855,8 +21758,8 @@
     <row r="100" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C100" s="1"/>
       <c r="D100" s="2"/>
-      <c r="E100" s="2" t="s">
-        <v>5</v>
+      <c r="E100" s="2">
+        <v>2</v>
       </c>
       <c r="F100" s="5">
         <v>10</v>
@@ -21869,8 +21772,8 @@
     <row r="101" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C101" s="1"/>
       <c r="D101" s="2"/>
-      <c r="E101" s="2" t="s">
-        <v>6</v>
+      <c r="E101" s="2">
+        <v>3</v>
       </c>
       <c r="F101" s="5">
         <v>10</v>
@@ -21883,8 +21786,8 @@
     <row r="102" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C102" s="1"/>
       <c r="D102" s="2"/>
-      <c r="E102" s="2" t="s">
-        <v>7</v>
+      <c r="E102" s="2">
+        <v>4</v>
       </c>
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
@@ -21895,8 +21798,8 @@
     <row r="103" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C103" s="1"/>
       <c r="D103" s="2"/>
-      <c r="E103" s="2" t="s">
-        <v>8</v>
+      <c r="E103" s="2">
+        <v>5</v>
       </c>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
@@ -21907,8 +21810,8 @@
     <row r="104" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C104" s="1"/>
       <c r="D104" s="2"/>
-      <c r="E104" s="2" t="s">
-        <v>9</v>
+      <c r="E104" s="2">
+        <v>6</v>
       </c>
       <c r="F104" s="5">
         <v>10</v>
@@ -21923,8 +21826,8 @@
     <row r="105" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C105" s="1"/>
       <c r="D105" s="2"/>
-      <c r="E105" s="2" t="s">
-        <v>10</v>
+      <c r="E105" s="2">
+        <v>7</v>
       </c>
       <c r="F105" s="5"/>
       <c r="G105" s="5">
@@ -21937,8 +21840,8 @@
     <row r="106" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C106" s="1"/>
       <c r="D106" s="2"/>
-      <c r="E106" s="2" t="s">
-        <v>11</v>
+      <c r="E106" s="2">
+        <v>8</v>
       </c>
       <c r="F106" s="5"/>
       <c r="G106" s="5">
@@ -21951,8 +21854,8 @@
     <row r="107" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C107" s="1"/>
       <c r="D107" s="2"/>
-      <c r="E107" s="2" t="s">
-        <v>12</v>
+      <c r="E107" s="2">
+        <v>9</v>
       </c>
       <c r="F107" s="5"/>
       <c r="G107" s="5">
@@ -21965,8 +21868,8 @@
     <row r="108" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C108" s="1"/>
       <c r="D108" s="2"/>
-      <c r="E108" s="2" t="s">
-        <v>13</v>
+      <c r="E108" s="2">
+        <v>10</v>
       </c>
       <c r="F108" s="5"/>
       <c r="G108" s="5">
@@ -21979,8 +21882,8 @@
     <row r="109" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C109" s="1"/>
       <c r="D109" s="2"/>
-      <c r="E109" s="2" t="s">
-        <v>14</v>
+      <c r="E109" s="2">
+        <v>11</v>
       </c>
       <c r="F109" s="5">
         <v>10</v>
@@ -21993,8 +21896,8 @@
     <row r="110" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C110" s="1"/>
       <c r="D110" s="2"/>
-      <c r="E110" s="2" t="s">
-        <v>15</v>
+      <c r="E110" s="2">
+        <v>12</v>
       </c>
       <c r="F110" s="5">
         <v>10</v>
@@ -22007,8 +21910,8 @@
     <row r="111" spans="3:8" x14ac:dyDescent="0.45">
       <c r="C111" s="1"/>
       <c r="D111" s="2"/>
-      <c r="E111" s="2" t="s">
-        <v>16</v>
+      <c r="E111" s="2">
+        <v>13</v>
       </c>
       <c r="F111" s="5"/>
       <c r="G111" s="5"/>
@@ -22018,8 +21921,8 @@
     </row>
     <row r="112" spans="3:8" x14ac:dyDescent="0.45">
       <c r="D112" s="2"/>
-      <c r="E112" s="2" t="s">
-        <v>17</v>
+      <c r="E112" s="2">
+        <v>14</v>
       </c>
       <c r="F112" s="5">
         <v>10</v>
@@ -22031,8 +21934,8 @@
     </row>
     <row r="113" spans="4:8" x14ac:dyDescent="0.45">
       <c r="D113" s="2"/>
-      <c r="E113" s="2" t="s">
-        <v>18</v>
+      <c r="E113" s="2">
+        <v>15</v>
       </c>
       <c r="F113" s="5"/>
       <c r="G113" s="5"/>
@@ -22042,8 +21945,8 @@
     </row>
     <row r="114" spans="4:8" x14ac:dyDescent="0.45">
       <c r="D114" s="2"/>
-      <c r="E114" s="2" t="s">
-        <v>19</v>
+      <c r="E114" s="2">
+        <v>16</v>
       </c>
       <c r="F114" s="5"/>
       <c r="G114" s="5">
@@ -22055,8 +21958,8 @@
     </row>
     <row r="115" spans="4:8" x14ac:dyDescent="0.45">
       <c r="D115" s="2"/>
-      <c r="E115" s="2" t="s">
-        <v>23</v>
+      <c r="E115" s="2">
+        <v>17</v>
       </c>
       <c r="F115" s="5">
         <v>10</v>
@@ -22068,8 +21971,8 @@
     </row>
     <row r="116" spans="4:8" x14ac:dyDescent="0.45">
       <c r="D116" s="2"/>
-      <c r="E116" s="2" t="s">
-        <v>24</v>
+      <c r="E116" s="2">
+        <v>18</v>
       </c>
       <c r="F116" s="5">
         <v>10</v>
